--- a/astro-site/public/dl/ice-cream-shop-business-plan/ice-cream-shop-startup-checklist.xlsx
+++ b/astro-site/public/dl/ice-cream-shop-business-plan/ice-cream-shop-startup-checklist.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Ask the city four things: whether the zoning allows making and selling ice cream with seating on site, how much electrical service the space has (ask the utility about 3-phase service and amps before signing), what ventilation the condenser units need (waffle cone irons need no smoke exhaust) and whether the street allows patio seating. Winter then runs on ice cream cakes, holiday pies and pints, hot chocolate and catering</t>
+          <t>Ask the city four things: whether the zoning allows making and selling ice cream with seating on site, how much electrical service the space has (ask the utility about 3-phase service and amps before signing), what ventilation the condenser units need (and whether the waffle cone irons need a hood: usually not) and whether the street allows patio seating</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Ask your state department of agriculture in writing. Buying pasteurized base from a licensed dairy (the case in this plan) usually needs a retail license. Making your own mix (the variant) means a state dairy plant or frozen dessert manufacturer license, 3-A equipment and inspections. Decide before you buy equipment, and ask your local health department what it expects</t>
+          <t>Ask your state department of agriculture in writing. Buying pasteurized base from a licensed dairy (the case in this plan) needs your retail food permit and, in some states (Vermont, for example), a frozen dessert license too. Making your own mix (the variant) means a state dairy plant or frozen dessert manufacturer license, 3-A equipment and inspections. Decide before you buy equipment, and ask your local health department what it expects</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Floor sink in the production room and an air outlet for the machines' condenser units. Waffle cone irons need no smoke exhaust</t>
+          <t>Floor sink in the production room and an air outlet for the machines' condenser units. Waffle cone irons usually need no exhaust hood: confirm it with the plan reviewer</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Receive the base at 41 °F (5 °C) or colder with lot codes and date marking. After the dairy's pasteurization you add only flavorings and mix-ins: no raw eggs, no raw milk or cream. If you pasteurize your own mix (the variant), fats, egg yolks and emulsifiers go in BEFORE pasteurization (155 °F for 30 minutes or 175 °F for 25 seconds), never after</t>
+          <t>Receive the base at 41 °F (5 °C) or colder with lot codes and date marking. After the dairy's pasteurization you add only flavorings and mix-ins: no raw eggs, no raw milk or cream. If you pasteurize your own mix (the variant), fats, egg yolks and emulsifiers go in BEFORE pasteurization (in Ohio, for example, 155 °F for 30 minutes or 175 °F for 25 seconds; your state sets its own), never after</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Two suppliers for each key ingredient (pistachio, cocoa, vanilla), packaging without expanded polystyrene, and paper or compostable spoons</t>
+          <t>Written agreement with the base supplier: delivery at 41 °F (5 °C) or colder, a lot code on every case and a copy of the dairy's license. Two suppliers for each key ingredient (pistachio, cocoa, vanilla), packaging without expanded polystyrene, and paper or compostable spoons</t>
         </is>
       </c>
     </row>
